--- a/Excel/AIStackEngineer.xlsx
+++ b/Excel/AIStackEngineer.xlsx
@@ -463,25 +463,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sCu34s8zb4o</t>
+          <t>-L_faOE-H5g</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OpenCode + AwesomeDesign-md:  Build 100X Stunning Designs for Free</t>
+          <t>OpenCode + Graphify: Stop Wasting Tokens in Opencode, Every Developer Use this</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29370</v>
+        <v>47566</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0:09:49</t>
+          <t>0:10:11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -493,25 +493,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-L_faOE-H5g</t>
+          <t>iYpHOxgZjUE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OpenCode + Graphify: Stop Wasting Tokens in Opencode, Every Developer Use this</t>
+          <t>Top 5 OpenCode Skills That Actually 100x Your Workflow (Free)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27527</v>
+        <v>43148</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0:10:11</t>
+          <t>0:13:41</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -523,25 +523,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>baGKgnbQUq8</t>
+          <t>sCu34s8zb4o</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Supercharge OpenCode With 1300+ Free Skills in One Command Makes It 100x  Powerful</t>
+          <t>OpenCode + AwesomeDesign-md:  Build 100X Stunning Designs for Free</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26297</v>
+        <v>38160</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0:09:53</t>
+          <t>0:09:49</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -553,25 +553,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>u9dg1d-r3RE</t>
+          <t>baGKgnbQUq8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OpenCode + GSD: The Free AI Coding Workflow to Build Real Projects 10X Better</t>
+          <t>Supercharge OpenCode With 1300+ Free Skills in One Command Makes It 100x  Powerful</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18032</v>
+        <v>37047</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0:12:05</t>
+          <t>0:09:53</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -583,25 +583,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEEDkAPNxFc</t>
+          <t>bhsd9MXfccg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OpenCode Second Brain: The OpenCode Setup Makes It 100x Smarter and Powerful</t>
+          <t>OpenCode + GitNexus: Give OpenCode Real Codebase Memory, Every Developer Use this</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17000</v>
+        <v>27163</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0:10:02</t>
+          <t>0:09:54</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -613,25 +613,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pc27ThkuBPQ</t>
+          <t>QIwLqXJkX08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OpenCode UI/UX Skill: Build 100X Better &amp; Modern Designs (100% Free)</t>
+          <t>OpenCode Persistent Memory Across Sessions, 10x Token Savings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14061</v>
+        <v>26991</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0:09:20</t>
+          <t>0:09:12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -643,25 +643,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5cmd-gC0bko</t>
+          <t>8yac_swVw8I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oh My OpenCode: #1 OpenCode Extension, Turns OpenCode Into a Full AI Dev Team</t>
+          <t>Pi Coding Agent: The Minimal Coding Agent That Beats Claude Code and OpenCode</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9112</v>
+        <v>25904</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0:10:16</t>
+          <t>0:08:19</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -673,25 +673,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>m8K-yCQ70VM</t>
+          <t>DEEDkAPNxFc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GLM 4.5 + OpenCode: The FREE Claude Code Alternative That Changes Everything!</t>
+          <t>OpenCode Second Brain: The OpenCode Setup Makes It 100x Smarter and Powerful</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7486</v>
+        <v>24688</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0:09:10</t>
+          <t>0:10:02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -703,25 +703,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e5sRVJTQxK8</t>
+          <t>xOOUEx8XBDE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pi Coding Agent: Forget Claude Code &amp; OpenCode — This Open Source Agent Is Insane</t>
+          <t>OpenCode + AionUi: Full Desktop AI Agent to Replace Claude Cowork for Free</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6353</v>
+        <v>24118</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0:09:18</t>
+          <t>0:09:02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -733,25 +733,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pUBALmdA33I</t>
+          <t>Pc27ThkuBPQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Turn Claude Code and OpenCode into Your Marketing Department (Free Skills)</t>
+          <t>OpenCode UI/UX Skill: Build 100X Better &amp; Modern Designs (100% Free)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5302</v>
+        <v>23948</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0:10:34</t>
+          <t>0:09:20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
